--- a/order_forms/050_retail_sampling_counter_order_form--order_forms.xlsx
+++ b/order_forms/050_retail_sampling_counter_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1174,8 +1174,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'product',_'value':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Product', 'value': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sample',_'value':_'sample'}</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sample', 'value': 'Sample'}</t>
+          <t>Sample</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'jimmy',_'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Jimmy', 'value': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'John', 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'store_1',_'value':_'store_1'}</t>
+          <t>store_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Store 1', 'value': 'Store 1'}</t>
+          <t>Store 1</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'store_2',_'value':_'store_2'}</t>
+          <t>store_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Store 2', 'value': 'Store 2'}</t>
+          <t>Store 2</t>
         </is>
       </c>
     </row>
